--- a/wwwroot/template/TemplateNCC.xlsx
+++ b/wwwroot/template/TemplateNCC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F70E0D-AE15-4D53-9DD5-D4645A074CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16695F0E-2A08-4C60-82A3-6F81875C1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{001D726D-0196-4D83-B98E-F8CF1E3B95C1}"/>
   </bookViews>
@@ -1055,18 +1055,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C79B0CD4-777B-4989-A23B-102DBDE470E9}">
-          <x14:formula1>
-            <xm:f>Sheet2!$A$1:$A$198</xm:f>
-          </x14:formula1>
-          <xm:sqref>A2:A512</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 

--- a/wwwroot/template/TemplateNCC.xlsx
+++ b/wwwroot/template/TemplateNCC.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16695F0E-2A08-4C60-82A3-6F81875C1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{001D726D-0196-4D83-B98E-F8CF1E3B95C1}"/>
+    <workbookView xWindow="5880" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{001D726D-0196-4D83-B98E-F8CF1E3B95C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
